--- a/inst/templates/Scenarios.xlsx
+++ b/inst/templates/Scenarios.xlsx
@@ -8,9 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="PKParameter" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="PKParameter" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,113 +19,10 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Pavel Balazki</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Pavel Balazki:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Simulation time is defined as time intervals.
-Expected is a triple of values {start, end, resolution}, resolution given in "points per &lt;time unit&gt;" as defined in the columne "SimulationTimeUnit". Multiple intervals can be separated by a ";"</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t xml:space="preserve">Scenario_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IndividualId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PopulationId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReadPopulationFromCSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelParameterSheets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ApplicationProtocol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SimulationTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SimulationTimeUnit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyState</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyStateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyStateTimeUnit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModelFile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OutputPathsIds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_scenario_male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aciclovir.pkml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_scenario_female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEMALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OutputPathId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OutputPath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aciclovir_PVB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organism|PeripheralVenousBlood|Aciclovir|Plasma (Peripheral Venous Blood)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aciclovir_fat_cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organism|Fat|Intracellular|Aciclovir|Concentration in container</t>
   </si>
   <si>
     <t xml:space="preserve">PKParameter</t>
@@ -140,7 +35,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,18 +66,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -226,12 +109,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -424,164 +311,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.29"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.57"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
